--- a/education_forms/042_datathon_registration_form--education_forms.xlsx
+++ b/education_forms/042_datathon_registration_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Datathon Name</t>
+          <t>Datathon Name 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Participant Email</t>
+          <t>Participant Email 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Participant Last Name</t>
+          <t>Participant Last Name 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Datathon Date</t>
+          <t>Datathon Date 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Participant First Name</t>
+          <t>Participant First Name 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Team Size</t>
+          <t>Team Size 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Participant Phone Number</t>
+          <t>Participant Phone Number 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Participant Email</t>
+          <t>Participant Email 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
